--- a/采集表.xlsx
+++ b/采集表.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>双碳实时数据采集系统</t>
+          <t>本安双碳实时数据采集系统</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>4360</t>
+          <t>4374</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>2729 / 1631</t>
+          <t>2743 / 1631</t>
         </is>
       </c>
       <c r="E5" s="4" t="n"/>
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>

--- a/采集表.xlsx
+++ b/采集表.xlsx
@@ -565,7 +565,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E4" s="4" t="n"/>
